--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8291,0.0659,0.0199,0.0234</t>
-  </si>
-  <si>
-    <t>0.6701,0.0446,0.0148,0.1478</t>
-  </si>
-  <si>
-    <t>0.8041,0.0182,0.0081,0.1002</t>
-  </si>
-  <si>
-    <t>0.7590,0.0184,0.0033,0.0977</t>
-  </si>
-  <si>
-    <t>0.7998,0.0644,0.0109,0.0282</t>
-  </si>
-  <si>
-    <t>0.6685,0.1433,0.0104,0.0258</t>
-  </si>
-  <si>
-    <t>0.6571,0.0599,0.0077,0.0671</t>
-  </si>
-  <si>
-    <t>0.6633,0.0641,0.0160,0.1178</t>
-  </si>
-  <si>
-    <t>0.8279,0.0396,0.0087,0.0399</t>
-  </si>
-  <si>
-    <t>0.7892,0.0465,0.0111,0.0582</t>
-  </si>
-  <si>
-    <t>0.6358,0.1857,0.0108,0.0184</t>
-  </si>
-  <si>
-    <t>0.8159,0.0193,0.0060,0.0800</t>
-  </si>
-  <si>
-    <t>0.8653,0.0346,0.0301,0.0314</t>
-  </si>
-  <si>
-    <t>0.9195,0.0095,0.0095,0.0347</t>
-  </si>
-  <si>
-    <t>0.9502,0.0059,0.0252,0.0072</t>
-  </si>
-  <si>
-    <t>0.9241,0.0102,0.0237,0.0242</t>
-  </si>
-  <si>
-    <t>0.8596,0.0459,0.0120,0.0163</t>
-  </si>
-  <si>
-    <t>0.0246,0.9193,0.0162,0.0276</t>
-  </si>
-  <si>
-    <t>0.1360,0.8282,0.0195,0.0110</t>
-  </si>
-  <si>
-    <t>0.7915,0.0818,0.0026,0.0120</t>
-  </si>
-  <si>
-    <t>0.3150,0.5399,0.0136,0.0204</t>
-  </si>
-  <si>
-    <t>0.1861,0.6064,0.0102,0.0385</t>
-  </si>
-  <si>
-    <t>0.9774,0.0029,0.0075,0.0027</t>
-  </si>
-  <si>
-    <t>0.9159,0.0101,0.0419,0.0074</t>
-  </si>
-  <si>
-    <t>0.8590,0.0022,0.2691,0.0013</t>
-  </si>
-  <si>
-    <t>0.5795,0.0616,0.3012,0.0808</t>
-  </si>
-  <si>
-    <t>0.8485,0.0457,0.0315,0.0292</t>
-  </si>
-  <si>
-    <t>0.7584,0.0427,0.2257,0.0158</t>
-  </si>
-  <si>
-    <t>0.7494,0.0353,0.2990,0.0064</t>
-  </si>
-  <si>
-    <t>0.7180,0.1393,0.0094,0.0241</t>
-  </si>
-  <si>
-    <t>0.8348,0.0399,0.0137,0.0361</t>
-  </si>
-  <si>
-    <t>0.0709,0.4581,0.8845,0.0087</t>
-  </si>
-  <si>
-    <t>0.7415,0.1361,0.0261,0.0252</t>
-  </si>
-  <si>
-    <t>0.7783,0.0405,0.0152,0.0719</t>
-  </si>
-  <si>
-    <t>0.6732,0.0366,0.0181,0.1867</t>
-  </si>
-  <si>
-    <t>0.8829,0.0507,0.0043,0.0085</t>
-  </si>
-  <si>
-    <t>0.3158,0.5348,0.0212,0.0160</t>
-  </si>
-  <si>
-    <t>0.7345,0.1039,0.0337,0.0567</t>
-  </si>
-  <si>
-    <t>0.8915,0.0054,0.0657,0.0225</t>
-  </si>
-  <si>
-    <t>0.9304,0.0009,0.0844,0.0019</t>
-  </si>
-  <si>
-    <t>0.8578,0.0057,0.1971,0.0034</t>
-  </si>
-  <si>
-    <t>0.3660,0.0773,0.5853,0.0211</t>
-  </si>
-  <si>
-    <t>0.4092,0.4766,0.0649,0.0201</t>
-  </si>
-  <si>
-    <t>0.8261,0.0080,0.0720,0.0786</t>
-  </si>
-  <si>
-    <t>0.5394,0.1733,0.0341,0.0817</t>
-  </si>
-  <si>
-    <t>0.4528,0.3302,0.0067,0.0200</t>
-  </si>
-  <si>
-    <t>0.6578,0.1794,0.0137,0.0213</t>
-  </si>
-  <si>
-    <t>0.6814,0.1783,0.0127,0.0214</t>
-  </si>
-  <si>
-    <t>0.2628,0.2289,0.6263,0.0404</t>
-  </si>
-  <si>
-    <t>0.5039,0.0556,0.5513,0.0058</t>
-  </si>
-  <si>
-    <t>0.8790,0.0226,0.0448,0.0233</t>
-  </si>
-  <si>
-    <t>0.9311,0.0031,0.0839,0.0025</t>
-  </si>
-  <si>
-    <t>0.2345,0.0315,0.9144,0.0010</t>
-  </si>
-  <si>
-    <t>0.6755,0.0192,0.3988,0.0054</t>
-  </si>
-  <si>
-    <t>0.6601,0.1737,0.0258,0.0369</t>
-  </si>
-  <si>
-    <t>0.6826,0.0401,0.0077,0.0925</t>
-  </si>
-  <si>
-    <t>0.8490,0.0138,0.0027,0.0483</t>
-  </si>
-  <si>
-    <t>0.3681,0.4008,0.2565,0.0797</t>
-  </si>
-  <si>
-    <t>0.5878,0.1285,0.0053,0.0323</t>
-  </si>
-  <si>
-    <t>0.7153,0.0656,0.0060,0.0458</t>
-  </si>
-  <si>
-    <t>0.8364,0.1259,0.0062,0.0050</t>
-  </si>
-  <si>
-    <t>0.0234,0.8458,0.8392,0.0062</t>
-  </si>
-  <si>
-    <t>0.4847,0.0330,0.6741,0.0024</t>
-  </si>
-  <si>
-    <t>0.6182,0.1146,0.2797,0.0291</t>
-  </si>
-  <si>
-    <t>0.0381,0.9161,0.4215,0.0040</t>
-  </si>
-  <si>
-    <t>0.2581,0.0590,0.7632,0.0104</t>
-  </si>
-  <si>
-    <t>0.3717,0.5489,0.0564,0.0160</t>
-  </si>
-  <si>
-    <t>0.0253,0.9795,0.0087,0.0009</t>
-  </si>
-  <si>
-    <t>0.8956,0.0499,0.0103,0.0103</t>
-  </si>
-  <si>
-    <t>0.7320,0.0679,0.0153,0.0549</t>
-  </si>
-  <si>
-    <t>0.0665,0.6780,0.7491,0.0129</t>
-  </si>
-  <si>
-    <t>0.2306,0.6804,0.2699,0.0059</t>
-  </si>
-  <si>
-    <t>0.5793,0.1505,0.2691,0.0485</t>
-  </si>
-  <si>
-    <t>0.0093,0.9490,0.7249,0.0041</t>
-  </si>
-  <si>
-    <t>0.0228,0.6502,0.9196,0.0094</t>
-  </si>
-  <si>
-    <t>0.8569,0.0068,0.0014,0.0681</t>
-  </si>
-  <si>
-    <t>0.5159,0.0515,0.0151,0.2815</t>
-  </si>
-  <si>
-    <t>0.8155,0.0024,0.0012,0.1938</t>
-  </si>
-  <si>
-    <t>0.6317,0.0146,0.0112,0.3641</t>
-  </si>
-  <si>
-    <t>0.8138,0.0146,0.0200,0.1465</t>
-  </si>
-  <si>
-    <t>0.8522,0.0071,0.0044,0.0996</t>
-  </si>
-  <si>
-    <t>0.3890,0.5159,0.0726,0.0179</t>
-  </si>
-  <si>
-    <t>0.4961,0.1406,0.4060,0.0152</t>
-  </si>
-  <si>
-    <t>0.5884,0.0456,0.4475,0.0070</t>
-  </si>
-  <si>
-    <t>0.0608,0.5164,0.8508,0.0080</t>
-  </si>
-  <si>
-    <t>0.1159,0.2106,0.7956,0.0115</t>
-  </si>
-  <si>
-    <t>0.0821,0.7820,0.6125,0.0083</t>
-  </si>
-  <si>
-    <t>0.7294,0.0453,0.0102,0.0774</t>
-  </si>
-  <si>
-    <t>0.7343,0.0705,0.0132,0.0505</t>
-  </si>
-  <si>
-    <t>0.8180,0.0528,0.0095,0.0242</t>
-  </si>
-  <si>
-    <t>0.6382,0.1072,0.0162,0.0627</t>
-  </si>
-  <si>
-    <t>0.8188,0.1114,0.0201,0.0113</t>
-  </si>
-  <si>
-    <t>0.7785,0.1134,0.0174,0.0218</t>
-  </si>
-  <si>
-    <t>0.5447,0.1859,0.0112,0.0397</t>
-  </si>
-  <si>
-    <t>0.6251,0.1210,0.0207,0.0696</t>
-  </si>
-  <si>
-    <t>0.7730,0.0624,0.0091,0.0367</t>
-  </si>
-  <si>
-    <t>0.8878,0.0700,0.0063,0.0083</t>
-  </si>
-  <si>
-    <t>0.7945,0.0575,0.0038,0.0215</t>
-  </si>
-  <si>
-    <t>0.8104,0.0443,0.0039,0.0246</t>
-  </si>
-  <si>
-    <t>0.8976,0.0160,0.0025,0.0238</t>
-  </si>
-  <si>
-    <t>0.6287,0.0732,0.0085,0.0709</t>
-  </si>
-  <si>
-    <t>0.7696,0.0401,0.0037,0.0312</t>
-  </si>
-  <si>
-    <t>0.6916,0.1009,0.0191,0.0638</t>
-  </si>
-  <si>
-    <t>0.1378,0.1269,0.8960,0.0065</t>
-  </si>
-  <si>
-    <t>0.2202,0.0518,0.7895,0.0035</t>
-  </si>
-  <si>
-    <t>0.9437,0.0096,0.0123,0.0105</t>
-  </si>
-  <si>
-    <t>0.4485,0.0354,0.6231,0.0121</t>
-  </si>
-  <si>
-    <t>0.2882,0.6450,0.0130,0.0133</t>
-  </si>
-  <si>
-    <t>0.2539,0.6408,0.0191,0.0219</t>
-  </si>
-  <si>
-    <t>0.0333,0.9266,0.0220,0.0095</t>
-  </si>
-  <si>
-    <t>0.3718,0.5694,0.0208,0.0099</t>
-  </si>
-  <si>
-    <t>0.1156,0.8112,0.0183,0.0159</t>
-  </si>
-  <si>
-    <t>0.0256,0.9430,0.0109,0.0113</t>
-  </si>
-  <si>
-    <t>0.6766,0.2384,0.0082,0.0078</t>
-  </si>
-  <si>
-    <t>0.8944,0.0257,0.0073,0.0193</t>
-  </si>
-  <si>
-    <t>0.8702,0.0123,0.0675,0.0266</t>
-  </si>
-  <si>
-    <t>0.7730,0.0571,0.1359,0.0433</t>
-  </si>
-  <si>
-    <t>0.9454,0.0100,0.0083,0.0131</t>
-  </si>
-  <si>
-    <t>0.5928,0.0729,0.0286,0.1783</t>
-  </si>
-  <si>
-    <t>0.3914,0.3257,0.0141,0.0353</t>
-  </si>
-  <si>
-    <t>0.9184,0.0295,0.0011,0.0058</t>
-  </si>
-  <si>
-    <t>0.3186,0.4959,0.0590,0.0311</t>
-  </si>
-  <si>
-    <t>0.0482,0.9647,0.0165,0.0014</t>
-  </si>
-  <si>
-    <t>0.7798,0.1832,0.0020,0.0024</t>
-  </si>
-  <si>
-    <t>0.5773,0.0410,0.0015,0.0778</t>
-  </si>
-  <si>
-    <t>0.5539,0.1035,0.0075,0.0607</t>
-  </si>
-  <si>
-    <t>0.8497,0.0745,0.0154,0.0097</t>
-  </si>
-  <si>
-    <t>0.7302,0.0885,0.0106,0.0335</t>
-  </si>
-  <si>
-    <t>0.7545,0.0500,0.0108,0.0643</t>
-  </si>
-  <si>
-    <t>0.6536,0.0524,0.0059,0.0864</t>
-  </si>
-  <si>
-    <t>0.7800,0.1360,0.0213,0.0193</t>
-  </si>
-  <si>
-    <t>0.8655,0.0332,0.0037,0.0203</t>
-  </si>
-  <si>
-    <t>0.7961,0.0280,0.0044,0.0487</t>
-  </si>
-  <si>
-    <t>0.6536,0.1738,0.0066,0.0134</t>
-  </si>
-  <si>
-    <t>0.6483,0.1405,0.2351,0.0062</t>
-  </si>
-  <si>
-    <t>0.6190,0.0779,0.3505,0.0132</t>
-  </si>
-  <si>
-    <t>0.3403,0.1014,0.6671,0.0082</t>
-  </si>
-  <si>
-    <t>0.6836,0.0961,0.1962,0.0173</t>
-  </si>
-  <si>
-    <t>0.9240,0.0078,0.0143,0.0220</t>
-  </si>
-  <si>
-    <t>0.8939,0.0376,0.0121,0.0216</t>
-  </si>
-  <si>
-    <t>0.8236,0.0409,0.0573,0.0479</t>
-  </si>
-  <si>
-    <t>0.8387,0.0456,0.0280,0.0394</t>
-  </si>
-  <si>
-    <t>0.9096,0.0082,0.0089,0.0472</t>
-  </si>
-  <si>
-    <t>0.5790,0.0051,0.0040,0.5343</t>
-  </si>
-  <si>
-    <t>0.8581,0.0086,0.0014,0.0631</t>
-  </si>
-  <si>
-    <t>0.8131,0.0106,0.0132,0.1318</t>
-  </si>
-  <si>
-    <t>0.0704,0.8597,0.3301,0.0144</t>
-  </si>
-  <si>
-    <t>0.8551,0.0187,0.0089,0.0737</t>
-  </si>
-  <si>
-    <t>0.6799,0.2044,0.0152,0.0174</t>
-  </si>
-  <si>
-    <t>0.9009,0.0169,0.0046,0.0255</t>
-  </si>
-  <si>
-    <t>0.7335,0.1311,0.0179,0.0226</t>
-  </si>
-  <si>
-    <t>0.8537,0.0267,0.0028,0.0263</t>
-  </si>
-  <si>
-    <t>0.8682,0.0090,0.0035,0.0825</t>
-  </si>
-  <si>
-    <t>0.7535,0.1139,0.0041,0.0108</t>
-  </si>
-  <si>
-    <t>0.0288,0.7698,0.8211,0.0145</t>
-  </si>
-  <si>
-    <t>0.9204,0.0120,0.0048,0.0215</t>
-  </si>
-  <si>
-    <t>0.7842,0.0396,0.0059,0.0386</t>
-  </si>
-  <si>
-    <t>0.6502,0.0499,0.0141,0.1146</t>
-  </si>
-  <si>
-    <t>0.8152,0.1067,0.0108,0.0138</t>
-  </si>
-  <si>
-    <t>0.7364,0.0608,0.0078,0.0524</t>
-  </si>
-  <si>
-    <t>0.5966,0.1915,0.0532,0.0548</t>
-  </si>
-  <si>
-    <t>0.8862,0.0263,0.0147,0.0203</t>
-  </si>
-  <si>
-    <t>0.8052,0.0546,0.0066,0.0262</t>
-  </si>
-  <si>
-    <t>0.8276,0.0533,0.0078,0.0228</t>
-  </si>
-  <si>
-    <t>0.5962,0.0934,0.0071,0.0659</t>
-  </si>
-  <si>
-    <t>0.8737,0.0522,0.0019,0.0065</t>
-  </si>
-  <si>
-    <t>0.7465,0.1049,0.0185,0.0300</t>
-  </si>
-  <si>
-    <t>0.7185,0.1028,0.0163,0.0396</t>
-  </si>
-  <si>
-    <t>0.7660,0.0175,0.0067,0.1397</t>
-  </si>
-  <si>
-    <t>0.6792,0.1558,0.0290,0.0500</t>
-  </si>
-  <si>
-    <t>0.7356,0.2238,0.0118,0.0068</t>
-  </si>
-  <si>
-    <t>0.6232,0.2080,0.0178,0.0251</t>
-  </si>
-  <si>
-    <t>0.4914,0.2395,0.0176,0.0451</t>
-  </si>
-  <si>
-    <t>0.4317,0.4779,0.0123,0.0100</t>
-  </si>
-  <si>
-    <t>0.7190,0.0908,0.0100,0.0415</t>
-  </si>
-  <si>
-    <t>0.3993,0.2785,0.0177,0.0627</t>
-  </si>
-  <si>
-    <t>0.7040,0.1436,0.0132,0.0160</t>
-  </si>
-  <si>
-    <t>0.8673,0.0703,0.0041,0.0069</t>
-  </si>
-  <si>
-    <t>0.7084,0.0421,0.0188,0.1401</t>
-  </si>
-  <si>
-    <t>0.0016,0.7483,0.9912,0.0002</t>
-  </si>
-  <si>
-    <t>0.8061,0.0652,0.0105,0.0234</t>
-  </si>
-  <si>
-    <t>0.3770,0.1174,0.6247,0.0038</t>
-  </si>
-  <si>
-    <t>0.5052,0.0494,0.5669,0.0123</t>
-  </si>
-  <si>
-    <t>0.8719,0.0142,0.1437,0.0069</t>
-  </si>
-  <si>
-    <t>0.3731,0.3684,0.3797,0.0810</t>
-  </si>
-  <si>
-    <t>0.7141,0.0075,0.4873,0.0016</t>
-  </si>
-  <si>
-    <t>0.4601,0.0636,0.5600,0.0202</t>
-  </si>
-  <si>
-    <t>0.4737,0.0447,0.5626,0.0150</t>
-  </si>
-  <si>
-    <t>0.9575,0.0031,0.0316,0.0028</t>
-  </si>
-  <si>
-    <t>0.9344,0.0119,0.0038,0.0116</t>
-  </si>
-  <si>
-    <t>0.7990,0.0346,0.0346,0.0823</t>
-  </si>
-  <si>
-    <t>0.8235,0.0522,0.0363,0.0380</t>
-  </si>
-  <si>
-    <t>0.8012,0.0443,0.1534,0.0202</t>
-  </si>
-  <si>
-    <t>0.8844,0.0127,0.0176,0.0313</t>
-  </si>
-  <si>
-    <t>0.9054,0.0104,0.0103,0.0307</t>
-  </si>
-  <si>
-    <t>0.8081,0.0266,0.0363,0.0815</t>
-  </si>
-  <si>
-    <t>0.5459,0.2414,0.0377,0.0545</t>
-  </si>
-  <si>
-    <t>0.3525,0.3031,0.0057,0.0285</t>
-  </si>
-  <si>
-    <t>0.2625,0.3925,0.0199,0.0672</t>
-  </si>
-  <si>
-    <t>0.8533,0.0236,0.0040,0.0345</t>
-  </si>
-  <si>
-    <t>0.5931,0.1441,0.0108,0.0377</t>
-  </si>
-  <si>
-    <t>0.8980,0.0139,0.0078,0.0430</t>
-  </si>
-  <si>
-    <t>0.9399,0.0096,0.0208,0.0057</t>
-  </si>
-  <si>
-    <t>0.9353,0.0123,0.0102,0.0082</t>
-  </si>
-  <si>
-    <t>0.9358,0.0046,0.0128,0.0246</t>
-  </si>
-  <si>
-    <t>0.8973,0.0207,0.0087,0.0232</t>
-  </si>
-  <si>
-    <t>0.0910,0.3142,0.8636,0.0094</t>
-  </si>
-  <si>
-    <t>0.8710,0.0451,0.0413,0.0121</t>
-  </si>
-  <si>
-    <t>0.8768,0.0619,0.0273,0.0139</t>
-  </si>
-  <si>
-    <t>0.8067,0.0068,0.2362,0.0067</t>
-  </si>
-  <si>
-    <t>0.5392,0.2393,0.2507,0.0109</t>
-  </si>
-  <si>
-    <t>0.7722,0.0273,0.0020,0.0407</t>
-  </si>
-  <si>
-    <t>0.7263,0.0628,0.0107,0.0620</t>
-  </si>
-  <si>
-    <t>0.6481,0.2464,0.0239,0.0161</t>
-  </si>
-  <si>
-    <t>0.7933,0.0367,0.0052,0.0478</t>
-  </si>
-  <si>
-    <t>0.7264,0.0177,0.0031,0.1333</t>
-  </si>
-  <si>
-    <t>0.7891,0.0296,0.0089,0.0729</t>
-  </si>
-  <si>
-    <t>0.7943,0.0830,0.0077,0.0212</t>
-  </si>
-  <si>
-    <t>0.5930,0.1125,0.0090,0.0513</t>
-  </si>
-  <si>
-    <t>0.7007,0.0835,0.1918,0.0531</t>
-  </si>
-  <si>
-    <t>0.8266,0.0419,0.0101,0.0351</t>
-  </si>
-  <si>
-    <t>0.6851,0.1656,0.0384,0.0425</t>
-  </si>
-  <si>
-    <t>0.5523,0.0217,0.5918,0.0032</t>
-  </si>
-  <si>
-    <t>0.2009,0.0250,0.7555,0.0340</t>
-  </si>
-  <si>
-    <t>0.8657,0.0159,0.1082,0.0115</t>
-  </si>
-  <si>
-    <t>0.1374,0.0244,0.9172,0.0020</t>
-  </si>
-  <si>
-    <t>0.6942,0.0401,0.2395,0.0369</t>
-  </si>
-  <si>
-    <t>0.3076,0.1711,0.6413,0.0235</t>
-  </si>
-  <si>
-    <t>0.3123,0.0260,0.7064,0.0113</t>
-  </si>
-  <si>
-    <t>0.7227,0.0239,0.0750,0.1395</t>
-  </si>
-  <si>
-    <t>0.9162,0.0212,0.0160,0.0087</t>
-  </si>
-  <si>
-    <t>0.9047,0.0111,0.0171,0.0332</t>
-  </si>
-  <si>
-    <t>0.8315,0.0229,0.0127,0.0650</t>
-  </si>
-  <si>
-    <t>0.6205,0.0732,0.0215,0.1501</t>
-  </si>
-  <si>
-    <t>0.7604,0.0274,0.0024,0.0608</t>
-  </si>
-  <si>
-    <t>0.7892,0.0346,0.0102,0.0806</t>
-  </si>
-  <si>
-    <t>0.7817,0.0759,0.0057,0.0188</t>
-  </si>
-  <si>
-    <t>0.6473,0.1520,0.0159,0.0352</t>
-  </si>
-  <si>
-    <t>0.2160,0.5320,0.0297,0.0584</t>
-  </si>
-  <si>
-    <t>0.8507,0.0476,0.0054,0.0166</t>
-  </si>
-  <si>
-    <t>0.7235,0.0299,0.0057,0.0934</t>
-  </si>
-  <si>
-    <t>0.7093,0.0264,0.3521,0.0065</t>
-  </si>
-  <si>
-    <t>0.0089,0.7888,0.9611,0.0015</t>
-  </si>
-  <si>
-    <t>0.7696,0.0134,0.2259,0.0231</t>
-  </si>
-  <si>
-    <t>0.6630,0.0492,0.3124,0.0254</t>
-  </si>
-  <si>
-    <t>0.5307,0.0039,0.6284,0.0033</t>
-  </si>
-  <si>
-    <t>0.8916,0.0130,0.0540,0.0228</t>
-  </si>
-  <si>
-    <t>0.9379,0.0157,0.0242,0.0085</t>
-  </si>
-  <si>
-    <t>0.8370,0.0255,0.0370,0.0826</t>
-  </si>
-  <si>
-    <t>0.9460,0.0074,0.0021,0.0136</t>
-  </si>
-  <si>
-    <t>0.8524,0.0046,0.0038,0.1201</t>
-  </si>
-  <si>
-    <t>0.7170,0.0495,0.0178,0.1384</t>
-  </si>
-  <si>
-    <t>0.7295,0.0133,0.0049,0.1677</t>
-  </si>
-  <si>
-    <t>0.6835,0.0071,0.0020,0.3000</t>
-  </si>
-  <si>
-    <t>0.8760,0.0145,0.0054,0.0494</t>
+    <t>0.9573,0.0020,0.0034,0.0332</t>
+  </si>
+  <si>
+    <t>0.0147,0.0003,0.0004,0.9957</t>
+  </si>
+  <si>
+    <t>0.9656,0.0006,0.0003,0.0478</t>
+  </si>
+  <si>
+    <t>0.0637,0.0059,0.0034,0.9672</t>
+  </si>
+  <si>
+    <t>0.9978,0.0002,0.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.9914,0.0021,0.0003,0.0022</t>
+  </si>
+  <si>
+    <t>0.9973,0.0003,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9936,0.0020,0.0006,0.0010</t>
+  </si>
+  <si>
+    <t>0.9930,0.0027,0.0005,0.0010</t>
+  </si>
+  <si>
+    <t>0.9879,0.0062,0.0024,0.0013</t>
+  </si>
+  <si>
+    <t>0.9947,0.0008,0.0003,0.0019</t>
+  </si>
+  <si>
+    <t>0.9936,0.0011,0.0003,0.0024</t>
+  </si>
+  <si>
+    <t>0.8929,0.0076,0.0850,0.0092</t>
+  </si>
+  <si>
+    <t>0.0254,0.0054,0.9743,0.0018</t>
+  </si>
+  <si>
+    <t>0.2760,0.0010,0.9125,0.0002</t>
+  </si>
+  <si>
+    <t>0.0254,0.0039,0.9706,0.0018</t>
+  </si>
+  <si>
+    <t>0.9819,0.0011,0.0163,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.0004,0.9981,0.0007,0.0022</t>
+  </si>
+  <si>
+    <t>0.0046,0.9902,0.0005,0.0014</t>
+  </si>
+  <si>
+    <t>0.0126,0.9820,0.0028,0.0011</t>
+  </si>
+  <si>
+    <t>0.0006,0.9975,0.0020,0.0009</t>
+  </si>
+  <si>
+    <t>0.7793,0.0022,0.3249,0.0032</t>
+  </si>
+  <si>
+    <t>0.0924,0.0055,0.9250,0.0049</t>
+  </si>
+  <si>
+    <t>0.0068,0.0005,0.9957,0.0003</t>
+  </si>
+  <si>
+    <t>0.0614,0.0258,0.9239,0.0079</t>
+  </si>
+  <si>
+    <t>0.2118,0.0350,0.8164,0.0109</t>
+  </si>
+  <si>
+    <t>0.4520,0.0035,0.7212,0.0023</t>
+  </si>
+  <si>
+    <t>0.0070,0.0027,0.9695,0.0431</t>
+  </si>
+  <si>
+    <t>0.7224,0.2228,0.0491,0.0029</t>
+  </si>
+  <si>
+    <t>0.6240,0.0902,0.3351,0.0110</t>
+  </si>
+  <si>
+    <t>0.0013,0.0304,0.9926,0.0065</t>
+  </si>
+  <si>
+    <t>0.0149,0.9821,0.0035,0.0002</t>
+  </si>
+  <si>
+    <t>0.9211,0.0259,0.0100,0.0239</t>
+  </si>
+  <si>
+    <t>0.8254,0.1042,0.0124,0.0356</t>
+  </si>
+  <si>
+    <t>0.8905,0.1667,0.0055,0.0012</t>
+  </si>
+  <si>
+    <t>0.0131,0.9785,0.0704,0.0019</t>
+  </si>
+  <si>
+    <t>0.0306,0.9531,0.0111,0.0004</t>
+  </si>
+  <si>
+    <t>0.2381,0.0036,0.4511,0.1114</t>
+  </si>
+  <si>
+    <t>0.0134,0.0155,0.9804,0.0017</t>
+  </si>
+  <si>
+    <t>0.4230,0.0020,0.8281,0.0006</t>
+  </si>
+  <si>
+    <t>0.0083,0.0288,0.9880,0.0012</t>
+  </si>
+  <si>
+    <t>0.0108,0.9735,0.0291,0.0037</t>
+  </si>
+  <si>
+    <t>0.0028,0.0024,0.9950,0.0011</t>
+  </si>
+  <si>
+    <t>0.0258,0.0290,0.0027,0.9759</t>
+  </si>
+  <si>
+    <t>0.0038,0.9930,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.0065,0.9759,0.0240,0.0062</t>
+  </si>
+  <si>
+    <t>0.0003,0.9981,0.0017,0.0011</t>
+  </si>
+  <si>
+    <t>0.0020,0.0056,0.9910,0.0032</t>
+  </si>
+  <si>
+    <t>0.0052,0.3574,0.9558,0.0039</t>
+  </si>
+  <si>
+    <t>0.0046,0.0028,0.9933,0.0004</t>
+  </si>
+  <si>
+    <t>0.0065,0.0012,0.9938,0.0008</t>
+  </si>
+  <si>
+    <t>0.0097,0.0167,0.9784,0.0089</t>
+  </si>
+  <si>
+    <t>0.0049,0.0160,0.9902,0.0006</t>
+  </si>
+  <si>
+    <t>0.9869,0.0081,0.0007,0.0011</t>
+  </si>
+  <si>
+    <t>0.9843,0.0004,0.0179,0.0006</t>
+  </si>
+  <si>
+    <t>0.9833,0.0090,0.0055,0.0016</t>
+  </si>
+  <si>
+    <t>0.0036,0.0123,0.9914,0.0093</t>
+  </si>
+  <si>
+    <t>0.9900,0.0024,0.0022,0.0017</t>
+  </si>
+  <si>
+    <t>0.9926,0.0020,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9075,0.1028,0.0145,0.0061</t>
+  </si>
+  <si>
+    <t>0.0002,0.9624,0.9890,0.0003</t>
+  </si>
+  <si>
+    <t>0.0006,0.0283,0.9944,0.0033</t>
+  </si>
+  <si>
+    <t>0.0030,0.0034,0.9828,0.0198</t>
+  </si>
+  <si>
+    <t>0.0012,0.7137,0.9889,0.0007</t>
+  </si>
+  <si>
+    <t>0.0007,0.0008,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0330,0.9628,0.0037,0.0003</t>
+  </si>
+  <si>
+    <t>0.0008,0.9979,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.7815,0.0252,0.3375,0.0107</t>
+  </si>
+  <si>
+    <t>0.4694,0.1092,0.2929,0.2754</t>
+  </si>
+  <si>
+    <t>0.0094,0.0028,0.9890,0.0014</t>
+  </si>
+  <si>
+    <t>0.0008,0.9498,0.9507,0.0006</t>
+  </si>
+  <si>
+    <t>0.0039,0.8791,0.6902,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.0298,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.9702,0.8352,0.0008</t>
+  </si>
+  <si>
+    <t>0.0030,0.0005,0.0074,0.9943</t>
+  </si>
+  <si>
+    <t>0.0002,0.0012,0.0002,0.9997</t>
+  </si>
+  <si>
+    <t>0.0029,0.0019,0.0002,0.9983</t>
+  </si>
+  <si>
+    <t>0.0072,0.0018,0.0032,0.9940</t>
+  </si>
+  <si>
+    <t>0.0010,0.0003,0.0005,0.9990</t>
+  </si>
+  <si>
+    <t>0.0024,0.0017,0.0012,0.9978</t>
+  </si>
+  <si>
+    <t>0.0003,0.9756,0.9248,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.9494,0.9837,0.0004</t>
+  </si>
+  <si>
+    <t>0.0055,0.9482,0.4777,0.0021</t>
+  </si>
+  <si>
+    <t>0.0014,0.8404,0.9692,0.0011</t>
+  </si>
+  <si>
+    <t>0.0033,0.9142,0.6565,0.0006</t>
+  </si>
+  <si>
+    <t>0.0025,0.9520,0.7157,0.0031</t>
+  </si>
+  <si>
+    <t>0.9920,0.0013,0.0004,0.0019</t>
+  </si>
+  <si>
+    <t>0.9804,0.0187,0.0018,0.0010</t>
+  </si>
+  <si>
+    <t>0.9950,0.0020,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9467,0.0152,0.0012,0.0154</t>
+  </si>
+  <si>
+    <t>0.9879,0.0046,0.0007,0.0018</t>
+  </si>
+  <si>
+    <t>0.9891,0.0032,0.0004,0.0025</t>
+  </si>
+  <si>
+    <t>0.9809,0.0161,0.0016,0.0008</t>
+  </si>
+  <si>
+    <t>0.9930,0.0029,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9983,0.0001,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9921,0.0033,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9933,0.0008,0.0012,0.0019</t>
+  </si>
+  <si>
+    <t>0.9964,0.0002,0.0003,0.0014</t>
+  </si>
+  <si>
+    <t>0.9921,0.0023,0.0007,0.0014</t>
+  </si>
+  <si>
+    <t>0.9855,0.0070,0.0046,0.0011</t>
+  </si>
+  <si>
+    <t>0.9972,0.0005,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9904,0.0011,0.0012,0.0042</t>
+  </si>
+  <si>
+    <t>0.0025,0.0015,0.9939,0.0039</t>
+  </si>
+  <si>
+    <t>0.0139,0.0101,0.9771,0.0013</t>
+  </si>
+  <si>
+    <t>0.9912,0.0014,0.0041,0.0002</t>
+  </si>
+  <si>
+    <t>0.0372,0.0011,0.9783,0.0005</t>
+  </si>
+  <si>
+    <t>0.0125,0.9825,0.0018,0.0014</t>
+  </si>
+  <si>
+    <t>0.0006,0.9971,0.0012,0.0009</t>
+  </si>
+  <si>
+    <t>0.0145,0.9747,0.0110,0.0088</t>
+  </si>
+  <si>
+    <t>0.0302,0.9671,0.0055,0.0029</t>
+  </si>
+  <si>
+    <t>0.0139,0.9859,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.0052,0.9928,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.8464,0.2629,0.0055,0.0013</t>
+  </si>
+  <si>
+    <t>0.8368,0.0311,0.1144,0.0181</t>
+  </si>
+  <si>
+    <t>0.7928,0.0019,0.4134,0.0008</t>
+  </si>
+  <si>
+    <t>0.2874,0.0211,0.7332,0.0199</t>
+  </si>
+  <si>
+    <t>0.8683,0.0084,0.2049,0.0016</t>
+  </si>
+  <si>
+    <t>0.0147,0.0743,0.0166,0.9700</t>
+  </si>
+  <si>
+    <t>0.0006,0.9966,0.0017,0.0020</t>
+  </si>
+  <si>
+    <t>0.0007,0.9962,0.0005,0.0032</t>
+  </si>
+  <si>
+    <t>0.0003,0.9969,0.0013,0.0100</t>
+  </si>
+  <si>
+    <t>0.0003,0.8881,0.9872,0.0003</t>
+  </si>
+  <si>
+    <t>0.0143,0.9841,0.0023,0.0005</t>
+  </si>
+  <si>
+    <t>0.7865,0.3128,0.0073,0.0020</t>
+  </si>
+  <si>
+    <t>0.8555,0.1888,0.0117,0.0062</t>
+  </si>
+  <si>
+    <t>0.9888,0.0061,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9909,0.0011,0.0065,0.0006</t>
+  </si>
+  <si>
+    <t>0.9862,0.0017,0.0014,0.0080</t>
+  </si>
+  <si>
+    <t>0.9907,0.0019,0.0034,0.0014</t>
+  </si>
+  <si>
+    <t>0.9925,0.0008,0.0017,0.0020</t>
+  </si>
+  <si>
+    <t>0.9954,0.0008,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9907,0.0014,0.0012,0.0028</t>
+  </si>
+  <si>
+    <t>0.9851,0.0018,0.0113,0.0016</t>
+  </si>
+  <si>
+    <t>0.0100,0.5010,0.9629,0.0011</t>
+  </si>
+  <si>
+    <t>0.0148,0.5427,0.8717,0.0022</t>
+  </si>
+  <si>
+    <t>0.0095,0.0279,0.9720,0.0005</t>
+  </si>
+  <si>
+    <t>0.0383,0.0184,0.9049,0.0138</t>
+  </si>
+  <si>
+    <t>0.9927,0.0018,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.9256,0.0077,0.0535,0.0050</t>
+  </si>
+  <si>
+    <t>0.4701,0.0017,0.7368,0.0015</t>
+  </si>
+  <si>
+    <t>0.8912,0.0447,0.0376,0.0132</t>
+  </si>
+  <si>
+    <t>0.0526,0.0012,0.0034,0.9773</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0004,0.9999</t>
+  </si>
+  <si>
+    <t>0.0013,0.0112,0.0035,0.9965</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.0014,0.9988</t>
+  </si>
+  <si>
+    <t>0.0057,0.3473,0.8986,0.0111</t>
+  </si>
+  <si>
+    <t>0.9950,0.0016,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.0049,0.9881,0.0007,0.0030</t>
+  </si>
+  <si>
+    <t>0.9880,0.0022,0.0030,0.0030</t>
+  </si>
+  <si>
+    <t>0.3037,0.5618,0.0011,0.0166</t>
+  </si>
+  <si>
+    <t>0.9783,0.0026,0.0019,0.0093</t>
+  </si>
+  <si>
+    <t>0.7777,0.0048,0.0025,0.2669</t>
+  </si>
+  <si>
+    <t>0.9909,0.0040,0.0020,0.0007</t>
+  </si>
+  <si>
+    <t>0.0003,0.1253,0.9939,0.0083</t>
+  </si>
+  <si>
+    <t>0.9137,0.0009,0.0011,0.1219</t>
+  </si>
+  <si>
+    <t>0.9396,0.0084,0.0321,0.0170</t>
+  </si>
+  <si>
+    <t>0.3999,0.6555,0.0143,0.0094</t>
+  </si>
+  <si>
+    <t>0.9850,0.0053,0.0043,0.0004</t>
+  </si>
+  <si>
+    <t>0.9722,0.0091,0.0095,0.0014</t>
+  </si>
+  <si>
+    <t>0.0342,0.9484,0.0113,0.0053</t>
+  </si>
+  <si>
+    <t>0.4523,0.1438,0.3812,0.0102</t>
+  </si>
+  <si>
+    <t>0.9200,0.0730,0.0144,0.0018</t>
+  </si>
+  <si>
+    <t>0.9902,0.0005,0.0013,0.0068</t>
+  </si>
+  <si>
+    <t>0.9907,0.0007,0.0003,0.0063</t>
+  </si>
+  <si>
+    <t>0.9859,0.0058,0.0029,0.0019</t>
+  </si>
+  <si>
+    <t>0.9862,0.0002,0.0003,0.0181</t>
+  </si>
+  <si>
+    <t>0.9905,0.0024,0.0022,0.0013</t>
+  </si>
+  <si>
+    <t>0.9877,0.0062,0.0024,0.0010</t>
+  </si>
+  <si>
+    <t>0.9798,0.0020,0.0182,0.0016</t>
+  </si>
+  <si>
+    <t>0.9965,0.0006,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.8170,0.2486,0.0033,0.0029</t>
+  </si>
+  <si>
+    <t>0.8400,0.2051,0.0019,0.0029</t>
+  </si>
+  <si>
+    <t>0.7229,0.3893,0.0021,0.0016</t>
+  </si>
+  <si>
+    <t>0.8681,0.1323,0.0112,0.0109</t>
+  </si>
+  <si>
+    <t>0.9769,0.0294,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.8763,0.1873,0.0031,0.0028</t>
+  </si>
+  <si>
+    <t>0.9801,0.0069,0.0057,0.0030</t>
+  </si>
+  <si>
+    <t>0.8879,0.1668,0.0021,0.0017</t>
+  </si>
+  <si>
+    <t>0.0017,0.0385,0.9970,0.0004</t>
+  </si>
+  <si>
+    <t>0.7175,0.3227,0.0273,0.0036</t>
+  </si>
+  <si>
+    <t>0.0026,0.0032,0.9942,0.0017</t>
+  </si>
+  <si>
+    <t>0.0444,0.0108,0.9665,0.0032</t>
+  </si>
+  <si>
+    <t>0.0086,0.0009,0.9948,0.0001</t>
+  </si>
+  <si>
+    <t>0.0105,0.0049,0.9881,0.0008</t>
+  </si>
+  <si>
+    <t>0.0038,0.0024,0.9945,0.0010</t>
+  </si>
+  <si>
+    <t>0.0053,0.0014,0.9963,0.0002</t>
+  </si>
+  <si>
+    <t>0.0031,0.0011,0.9953,0.0011</t>
+  </si>
+  <si>
+    <t>0.3578,0.0022,0.8432,0.0008</t>
+  </si>
+  <si>
+    <t>0.0444,0.0131,0.9596,0.0013</t>
+  </si>
+  <si>
+    <t>0.6017,0.1247,0.2371,0.0190</t>
+  </si>
+  <si>
+    <t>0.0820,0.2179,0.5859,0.0267</t>
+  </si>
+  <si>
+    <t>0.5490,0.0219,0.5664,0.0017</t>
+  </si>
+  <si>
+    <t>0.8201,0.0158,0.1822,0.0048</t>
+  </si>
+  <si>
+    <t>0.2329,0.0070,0.8461,0.0051</t>
+  </si>
+  <si>
+    <t>0.2773,0.0493,0.6931,0.0179</t>
+  </si>
+  <si>
+    <t>0.0486,0.9481,0.0036,0.0073</t>
+  </si>
+  <si>
+    <t>0.1237,0.9201,0.0018,0.0017</t>
+  </si>
+  <si>
+    <t>0.0844,0.9461,0.0011,0.0015</t>
+  </si>
+  <si>
+    <t>0.9459,0.0876,0.0013,0.0008</t>
+  </si>
+  <si>
+    <t>0.8958,0.2169,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.6503,0.0898,0.2147,0.0111</t>
+  </si>
+  <si>
+    <t>0.9108,0.0035,0.1357,0.0013</t>
+  </si>
+  <si>
+    <t>0.9318,0.0079,0.0428,0.0061</t>
+  </si>
+  <si>
+    <t>0.6187,0.0196,0.3283,0.0601</t>
+  </si>
+  <si>
+    <t>0.9678,0.0031,0.0178,0.0032</t>
+  </si>
+  <si>
+    <t>0.0037,0.0030,0.9916,0.0026</t>
+  </si>
+  <si>
+    <t>0.0234,0.4298,0.7932,0.0103</t>
+  </si>
+  <si>
+    <t>0.0704,0.0088,0.9273,0.0091</t>
+  </si>
+  <si>
+    <t>0.1477,0.0084,0.8794,0.0085</t>
+  </si>
+  <si>
+    <t>0.0098,0.7640,0.6284,0.0006</t>
+  </si>
+  <si>
+    <t>0.9886,0.0036,0.0009,0.0020</t>
+  </si>
+  <si>
+    <t>0.9729,0.0136,0.0122,0.0030</t>
+  </si>
+  <si>
+    <t>0.9922,0.0018,0.0010,0.0017</t>
+  </si>
+  <si>
+    <t>0.9922,0.0062,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9258,0.1169,0.0033,0.0016</t>
+  </si>
+  <si>
+    <t>0.9952,0.0017,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9873,0.0015,0.0021,0.0052</t>
+  </si>
+  <si>
+    <t>0.9915,0.0014,0.0019,0.0021</t>
+  </si>
+  <si>
+    <t>0.0111,0.0190,0.9826,0.0041</t>
+  </si>
+  <si>
+    <t>0.5387,0.0728,0.4757,0.0062</t>
+  </si>
+  <si>
+    <t>0.1427,0.0093,0.7798,0.0918</t>
+  </si>
+  <si>
+    <t>0.0079,0.0183,0.9889,0.0004</t>
+  </si>
+  <si>
+    <t>0.0115,0.0167,0.8990,0.1380</t>
+  </si>
+  <si>
+    <t>0.0099,0.0140,0.9732,0.0117</t>
+  </si>
+  <si>
+    <t>0.0005,0.0008,0.9975,0.0018</t>
+  </si>
+  <si>
+    <t>0.0084,0.0379,0.9677,0.0006</t>
+  </si>
+  <si>
+    <t>0.0023,0.0025,0.9929,0.0041</t>
+  </si>
+  <si>
+    <t>0.0066,0.0030,0.9859,0.0055</t>
+  </si>
+  <si>
+    <t>0.0333,0.1501,0.8497,0.0055</t>
+  </si>
+  <si>
+    <t>0.9226,0.0023,0.0785,0.0068</t>
+  </si>
+  <si>
+    <t>0.9151,0.0016,0.1204,0.0026</t>
+  </si>
+  <si>
+    <t>0.9215,0.0019,0.0447,0.0184</t>
+  </si>
+  <si>
+    <t>0.9912,0.0036,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9859,0.0082,0.0028,0.0011</t>
+  </si>
+  <si>
+    <t>0.9966,0.0015,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9773,0.0321,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9946,0.0005,0.0006,0.0014</t>
+  </si>
+  <si>
+    <t>0.9776,0.0105,0.0070,0.0024</t>
+  </si>
+  <si>
+    <t>0.9664,0.0247,0.0066,0.0029</t>
+  </si>
+  <si>
+    <t>0.9859,0.0059,0.0009,0.0026</t>
+  </si>
+  <si>
+    <t>0.0050,0.0056,0.9886,0.0008</t>
+  </si>
+  <si>
+    <t>0.0015,0.0202,0.9923,0.0010</t>
+  </si>
+  <si>
+    <t>0.0066,0.0448,0.9844,0.0030</t>
+  </si>
+  <si>
+    <t>0.0451,0.1031,0.8484,0.0377</t>
+  </si>
+  <si>
+    <t>0.0055,0.0011,0.9932,0.0012</t>
+  </si>
+  <si>
+    <t>0.0483,0.0166,0.7840,0.2154</t>
+  </si>
+  <si>
+    <t>0.0606,0.0067,0.9447,0.0060</t>
+  </si>
+  <si>
+    <t>0.0068,0.0022,0.9798,0.0130</t>
+  </si>
+  <si>
+    <t>0.9846,0.0003,0.0008,0.0149</t>
+  </si>
+  <si>
+    <t>0.0599,0.0017,0.0003,0.9808</t>
+  </si>
+  <si>
+    <t>0.0098,0.0011,0.0106,0.9884</t>
+  </si>
+  <si>
+    <t>0.0013,0.0000,0.0001,0.9996</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.0003,0.9992</t>
+  </si>
+  <si>
+    <t>0.9502,0.0019,0.0017,0.0455</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3577,7 +3577,7 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
         <v>380</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4459,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
         <v>443</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
         <v>448</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4669,7 +4669,7 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
         <v>458</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4725,7 +4725,7 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
         <v>462</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5047,7 +5047,7 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D223" t="s">
         <v>485</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5285,7 +5285,7 @@
         <v>259</v>
       </c>
       <c r="C240" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D240" t="s">
         <v>502</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
